--- a/backend/data/financials_by_company/1707.HK.xlsx
+++ b/backend/data/financials_by_company/1707.HK.xlsx
@@ -647,57 +647,59 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>3960</v>
+        <v>1021020</v>
       </c>
       <c r="C2" t="n">
         <v>0.165</v>
       </c>
       <c r="D2" t="n">
-        <v>-13546000</v>
+        <v>-17994000</v>
       </c>
       <c r="E2" t="n">
-        <v>24000</v>
+        <v>6188000</v>
       </c>
       <c r="F2" t="n">
-        <v>24000</v>
+        <v>6188000</v>
       </c>
       <c r="G2" t="n">
-        <v>-15811000</v>
+        <v>-14280000</v>
       </c>
       <c r="H2" t="n">
-        <v>1937000</v>
+        <v>1761000</v>
       </c>
       <c r="I2" t="n">
-        <v>75113000</v>
+        <v>381759000</v>
       </c>
       <c r="J2" t="n">
-        <v>-13522000</v>
+        <v>-11806000</v>
       </c>
       <c r="K2" t="n">
-        <v>-15459000</v>
+        <v>-13567000</v>
       </c>
       <c r="L2" t="n">
-        <v>2238000</v>
+        <v>266000</v>
       </c>
       <c r="M2" t="n">
-        <v>67000</v>
+        <v>50000</v>
       </c>
       <c r="N2" t="n">
-        <v>2305000</v>
+        <v>316000</v>
       </c>
       <c r="O2" t="n">
-        <v>-15831040</v>
+        <v>-19446980</v>
       </c>
       <c r="P2" t="n">
-        <v>-15811000</v>
+        <v>-14280000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99626000</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>408763000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>406000</v>
+      </c>
       <c r="S2" t="n">
         <v>1680000000</v>
       </c>
@@ -705,135 +707,135 @@
         <v>1680000000</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0094</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.0094</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="W2" t="n">
-        <v>-15811000</v>
+        <v>-14280000</v>
       </c>
       <c r="X2" t="n">
-        <v>-15811000</v>
+        <v>-14280000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-15811000</v>
+        <v>-14280000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-15811000</v>
+        <v>-14280000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-15811000</v>
+        <v>-14280000</v>
       </c>
       <c r="AC2" t="n">
-        <v>285000</v>
+        <v>663000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-15526000</v>
+        <v>-13617000</v>
       </c>
       <c r="AE2" t="n">
-        <v>1337000</v>
+        <v>4293000</v>
       </c>
       <c r="AF2" t="n">
-        <v>24000</v>
+        <v>6188000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-3000</v>
+        <v>-455000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-21000</v>
+        <v>-5733000</v>
       </c>
       <c r="AI2" t="n">
-        <v>2238000</v>
+        <v>266000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>67000</v>
+        <v>50000</v>
       </c>
       <c r="AK2" t="n">
-        <v>2305000</v>
+        <v>316000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-19125000</v>
+        <v>-24364000</v>
       </c>
       <c r="AM2" t="n">
-        <v>24513000</v>
+        <v>27004000</v>
       </c>
       <c r="AN2" t="n">
-        <v>24513000</v>
+        <v>27104000</v>
       </c>
       <c r="AO2" t="n">
-        <v>24513000</v>
+        <v>27104000</v>
       </c>
       <c r="AP2" t="n">
-        <v>5388000</v>
+        <v>2640000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>75113000</v>
+        <v>381759000</v>
       </c>
       <c r="AR2" t="n">
-        <v>80501000</v>
+        <v>384399000</v>
       </c>
       <c r="AS2" t="n">
-        <v>80501000</v>
+        <v>384399000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>46695</v>
+        <v>-64028.799703</v>
       </c>
       <c r="C3" t="n">
-        <v>0.165</v>
+        <v>0.00353</v>
       </c>
       <c r="D3" t="n">
-        <v>-16139000</v>
+        <v>-13590000</v>
       </c>
       <c r="E3" t="n">
-        <v>283000</v>
+        <v>-18137000</v>
       </c>
       <c r="F3" t="n">
-        <v>283000</v>
+        <v>-18137000</v>
       </c>
       <c r="G3" t="n">
-        <v>-16366000</v>
+        <v>-32178000</v>
       </c>
       <c r="H3" t="n">
-        <v>458000</v>
+        <v>523000</v>
       </c>
       <c r="I3" t="n">
-        <v>130989000</v>
+        <v>277743000</v>
       </c>
       <c r="J3" t="n">
-        <v>-15856000</v>
+        <v>-31727000</v>
       </c>
       <c r="K3" t="n">
-        <v>-16314000</v>
+        <v>-32250000</v>
       </c>
       <c r="L3" t="n">
-        <v>2460000</v>
+        <v>703000</v>
       </c>
       <c r="M3" t="n">
-        <v>35000</v>
+        <v>42000</v>
       </c>
       <c r="N3" t="n">
-        <v>2495000</v>
+        <v>745000</v>
       </c>
       <c r="O3" t="n">
-        <v>-16602305</v>
+        <v>-14105028.799703</v>
       </c>
       <c r="P3" t="n">
-        <v>-16366000</v>
+        <v>-32178000</v>
       </c>
       <c r="Q3" t="n">
-        <v>156036000</v>
+        <v>299505000</v>
       </c>
       <c r="R3" t="n">
-        <v>572000</v>
+        <v>486000</v>
       </c>
       <c r="S3" t="n">
         <v>1680000000</v>
@@ -842,133 +844,135 @@
         <v>1680000000</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0097</v>
+        <v>-0.0192</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0097</v>
+        <v>-0.0192</v>
       </c>
       <c r="W3" t="n">
-        <v>-16366000</v>
+        <v>-32178000</v>
       </c>
       <c r="X3" t="n">
-        <v>-16366000</v>
+        <v>-32178000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-16366000</v>
+        <v>-32178000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-16366000</v>
+        <v>-32178000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-16366000</v>
+        <v>-32178000</v>
       </c>
       <c r="AC3" t="n">
-        <v>17000</v>
+        <v>-114000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-16349000</v>
+        <v>-32292000</v>
       </c>
       <c r="AE3" t="n">
-        <v>2348000</v>
+        <v>3135000</v>
       </c>
       <c r="AF3" t="n">
-        <v>283000</v>
-      </c>
-      <c r="AG3" t="inlineStr"/>
+        <v>-18137000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-224000</v>
+      </c>
       <c r="AH3" t="n">
-        <v>-283000</v>
+        <v>18361000</v>
       </c>
       <c r="AI3" t="n">
-        <v>2460000</v>
+        <v>703000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>35000</v>
+        <v>42000</v>
       </c>
       <c r="AK3" t="n">
-        <v>2495000</v>
+        <v>745000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-21469000</v>
+        <v>-17993000</v>
       </c>
       <c r="AM3" t="n">
-        <v>25047000</v>
+        <v>21762000</v>
       </c>
       <c r="AN3" t="n">
-        <v>25047000</v>
+        <v>23518000</v>
       </c>
       <c r="AO3" t="n">
-        <v>25047000</v>
+        <v>23518000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3578000</v>
+        <v>3769000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>130989000</v>
+        <v>277743000</v>
       </c>
       <c r="AR3" t="n">
-        <v>134567000</v>
+        <v>281512000</v>
       </c>
       <c r="AS3" t="n">
-        <v>134567000</v>
+        <v>281512000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-64028.799703</v>
+        <v>46695</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00353</v>
+        <v>0.165</v>
       </c>
       <c r="D4" t="n">
-        <v>-13590000</v>
+        <v>-16139000</v>
       </c>
       <c r="E4" t="n">
-        <v>-18137000</v>
+        <v>283000</v>
       </c>
       <c r="F4" t="n">
-        <v>-18137000</v>
+        <v>283000</v>
       </c>
       <c r="G4" t="n">
-        <v>-32178000</v>
+        <v>-16366000</v>
       </c>
       <c r="H4" t="n">
-        <v>523000</v>
+        <v>458000</v>
       </c>
       <c r="I4" t="n">
-        <v>277743000</v>
+        <v>130989000</v>
       </c>
       <c r="J4" t="n">
-        <v>-31727000</v>
+        <v>-15856000</v>
       </c>
       <c r="K4" t="n">
-        <v>-32250000</v>
+        <v>-16314000</v>
       </c>
       <c r="L4" t="n">
-        <v>703000</v>
+        <v>2460000</v>
       </c>
       <c r="M4" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="N4" t="n">
-        <v>745000</v>
+        <v>2495000</v>
       </c>
       <c r="O4" t="n">
-        <v>-14105028.799703</v>
+        <v>-16602305</v>
       </c>
       <c r="P4" t="n">
-        <v>-32178000</v>
+        <v>-16366000</v>
       </c>
       <c r="Q4" t="n">
-        <v>299505000</v>
+        <v>156036000</v>
       </c>
       <c r="R4" t="n">
-        <v>486000</v>
+        <v>572000</v>
       </c>
       <c r="S4" t="n">
         <v>1680000000</v>
@@ -977,136 +981,132 @@
         <v>1680000000</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0192</v>
+        <v>-0.0097</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.0192</v>
+        <v>-0.0097</v>
       </c>
       <c r="W4" t="n">
-        <v>-32178000</v>
+        <v>-16366000</v>
       </c>
       <c r="X4" t="n">
-        <v>-32178000</v>
+        <v>-16366000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-32178000</v>
+        <v>-16366000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-32178000</v>
+        <v>-16366000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-32178000</v>
+        <v>-16366000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-114000</v>
+        <v>17000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-32292000</v>
+        <v>-16349000</v>
       </c>
       <c r="AE4" t="n">
-        <v>3135000</v>
+        <v>2348000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-18137000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-224000</v>
-      </c>
+        <v>283000</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>18361000</v>
+        <v>-283000</v>
       </c>
       <c r="AI4" t="n">
-        <v>703000</v>
+        <v>2460000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="AK4" t="n">
-        <v>745000</v>
+        <v>2495000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-17993000</v>
+        <v>-21469000</v>
       </c>
       <c r="AM4" t="n">
-        <v>21762000</v>
+        <v>25047000</v>
       </c>
       <c r="AN4" t="n">
-        <v>23518000</v>
+        <v>25047000</v>
       </c>
       <c r="AO4" t="n">
-        <v>23518000</v>
+        <v>25047000</v>
       </c>
       <c r="AP4" t="n">
-        <v>3769000</v>
+        <v>3578000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>277743000</v>
+        <v>130989000</v>
       </c>
       <c r="AR4" t="n">
-        <v>281512000</v>
+        <v>134567000</v>
       </c>
       <c r="AS4" t="n">
-        <v>281512000</v>
+        <v>134567000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>1021020</v>
+        <v>3960</v>
       </c>
       <c r="C5" t="n">
         <v>0.165</v>
       </c>
       <c r="D5" t="n">
-        <v>-17994000</v>
+        <v>-13546000</v>
       </c>
       <c r="E5" t="n">
-        <v>6188000</v>
+        <v>24000</v>
       </c>
       <c r="F5" t="n">
-        <v>6188000</v>
+        <v>24000</v>
       </c>
       <c r="G5" t="n">
-        <v>-14280000</v>
+        <v>-15811000</v>
       </c>
       <c r="H5" t="n">
-        <v>1761000</v>
+        <v>1937000</v>
       </c>
       <c r="I5" t="n">
-        <v>381759000</v>
+        <v>75113000</v>
       </c>
       <c r="J5" t="n">
-        <v>-11806000</v>
+        <v>-13522000</v>
       </c>
       <c r="K5" t="n">
-        <v>-13567000</v>
+        <v>-15459000</v>
       </c>
       <c r="L5" t="n">
-        <v>266000</v>
+        <v>2238000</v>
       </c>
       <c r="M5" t="n">
-        <v>50000</v>
+        <v>67000</v>
       </c>
       <c r="N5" t="n">
-        <v>316000</v>
+        <v>2305000</v>
       </c>
       <c r="O5" t="n">
-        <v>-19446980</v>
+        <v>-15831040</v>
       </c>
       <c r="P5" t="n">
-        <v>-14280000</v>
+        <v>-15811000</v>
       </c>
       <c r="Q5" t="n">
-        <v>408763000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>406000</v>
-      </c>
+        <v>99626000</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
         <v>1680000000</v>
       </c>
@@ -1114,79 +1114,79 @@
         <v>1680000000</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0094</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0094</v>
       </c>
       <c r="W5" t="n">
-        <v>-14280000</v>
+        <v>-15811000</v>
       </c>
       <c r="X5" t="n">
-        <v>-14280000</v>
+        <v>-15811000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>-14280000</v>
+        <v>-15811000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-14280000</v>
+        <v>-15811000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-14280000</v>
+        <v>-15811000</v>
       </c>
       <c r="AC5" t="n">
-        <v>663000</v>
+        <v>285000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-13617000</v>
+        <v>-15526000</v>
       </c>
       <c r="AE5" t="n">
-        <v>4293000</v>
+        <v>1337000</v>
       </c>
       <c r="AF5" t="n">
-        <v>6188000</v>
+        <v>24000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-455000</v>
+        <v>-3000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-5733000</v>
+        <v>-21000</v>
       </c>
       <c r="AI5" t="n">
-        <v>266000</v>
+        <v>2238000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>50000</v>
+        <v>67000</v>
       </c>
       <c r="AK5" t="n">
-        <v>316000</v>
+        <v>2305000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-24364000</v>
+        <v>-19125000</v>
       </c>
       <c r="AM5" t="n">
-        <v>27004000</v>
+        <v>24513000</v>
       </c>
       <c r="AN5" t="n">
-        <v>27104000</v>
+        <v>24513000</v>
       </c>
       <c r="AO5" t="n">
-        <v>27104000</v>
+        <v>24513000</v>
       </c>
       <c r="AP5" t="n">
-        <v>2640000</v>
+        <v>5388000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>381759000</v>
+        <v>75113000</v>
       </c>
       <c r="AR5" t="n">
-        <v>384399000</v>
+        <v>80501000</v>
       </c>
       <c r="AS5" t="n">
-        <v>384399000</v>
+        <v>80501000</v>
       </c>
     </row>
   </sheetData>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>1680000000</v>
@@ -1461,37 +1461,37 @@
         <v>1680000000</v>
       </c>
       <c r="D2" t="n">
-        <v>675000</v>
+        <v>1440000</v>
       </c>
       <c r="E2" t="n">
-        <v>161471000</v>
+        <v>225688000</v>
       </c>
       <c r="F2" t="n">
-        <v>161471000</v>
+        <v>225688000</v>
       </c>
       <c r="G2" t="n">
-        <v>158767000</v>
+        <v>224149000</v>
       </c>
       <c r="H2" t="n">
-        <v>161471000</v>
+        <v>225688000</v>
       </c>
       <c r="I2" t="n">
-        <v>675000</v>
+        <v>1440000</v>
       </c>
       <c r="J2" t="n">
-        <v>161471000</v>
+        <v>225688000</v>
       </c>
       <c r="K2" t="n">
-        <v>161471000</v>
+        <v>225688000</v>
       </c>
       <c r="L2" t="n">
-        <v>161471000</v>
+        <v>225688000</v>
       </c>
       <c r="M2" t="n">
-        <v>161471000</v>
+        <v>225688000</v>
       </c>
       <c r="N2" t="n">
-        <v>-32606000</v>
+        <v>31446000</v>
       </c>
       <c r="O2" t="n">
         <v>167266000</v>
@@ -1503,102 +1503,106 @@
         <v>16800000</v>
       </c>
       <c r="R2" t="n">
-        <v>26857000</v>
+        <v>74335000</v>
       </c>
       <c r="S2" t="n">
-        <v>741000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>741000</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
+        <v>605000</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>89000</v>
+      </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>516000</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>516000</v>
       </c>
       <c r="X2" t="n">
-        <v>26116000</v>
+        <v>73730000</v>
       </c>
       <c r="Y2" t="n">
-        <v>675000</v>
+        <v>924000</v>
       </c>
       <c r="Z2" t="n">
-        <v>675000</v>
+        <v>924000</v>
       </c>
       <c r="AA2" t="n">
-        <v>15510000</v>
+        <v>66561000</v>
       </c>
       <c r="AB2" t="n">
-        <v>71000</v>
+        <v>239000</v>
       </c>
       <c r="AC2" t="n">
-        <v>15439000</v>
+        <v>66322000</v>
       </c>
       <c r="AD2" t="n">
-        <v>188328000</v>
+        <v>300023000</v>
       </c>
       <c r="AE2" t="n">
-        <v>3445000</v>
+        <v>2144000</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
+        <v>1286000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1286000</v>
+      </c>
       <c r="AI2" t="n">
-        <v>3445000</v>
+        <v>858000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-6423000</v>
+        <v>-7408000</v>
       </c>
       <c r="AK2" t="n">
-        <v>9868000</v>
+        <v>8266000</v>
       </c>
       <c r="AL2" t="n">
-        <v>7570000</v>
+        <v>6144000</v>
       </c>
       <c r="AM2" t="n">
-        <v>2298000</v>
+        <v>2122000</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>184883000</v>
+        <v>297879000</v>
       </c>
       <c r="AP2" t="n">
-        <v>8971000</v>
+        <v>15669000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>38126000</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
+        <v>47988000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>35000</v>
+      </c>
       <c r="AS2" t="n">
-        <v>16173000</v>
+        <v>47915000</v>
       </c>
       <c r="AT2" t="n">
-        <v>-110000</v>
+        <v>-697000</v>
       </c>
       <c r="AU2" t="n">
-        <v>16283000</v>
+        <v>48612000</v>
       </c>
       <c r="AV2" t="n">
-        <v>121407000</v>
+        <v>186272000</v>
       </c>
       <c r="AW2" t="n">
-        <v>121407000</v>
+        <v>186272000</v>
       </c>
       <c r="AX2" t="n">
-        <v>121407000</v>
+        <v>186272000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>1680000000</v>
@@ -1607,37 +1611,37 @@
         <v>1680000000</v>
       </c>
       <c r="D3" t="n">
-        <v>1384000</v>
+        <v>516000</v>
       </c>
       <c r="E3" t="n">
-        <v>176930000</v>
+        <v>193224000</v>
       </c>
       <c r="F3" t="n">
-        <v>176930000</v>
+        <v>193224000</v>
       </c>
       <c r="G3" t="n">
-        <v>171457000</v>
+        <v>192407000</v>
       </c>
       <c r="H3" t="n">
-        <v>176930000</v>
+        <v>193224000</v>
       </c>
       <c r="I3" t="n">
-        <v>1384000</v>
+        <v>516000</v>
       </c>
       <c r="J3" t="n">
-        <v>176930000</v>
+        <v>193224000</v>
       </c>
       <c r="K3" t="n">
-        <v>176930000</v>
+        <v>193224000</v>
       </c>
       <c r="L3" t="n">
-        <v>176930000</v>
+        <v>193224000</v>
       </c>
       <c r="M3" t="n">
-        <v>176930000</v>
+        <v>193224000</v>
       </c>
       <c r="N3" t="n">
-        <v>-17098000</v>
+        <v>-732000</v>
       </c>
       <c r="O3" t="n">
         <v>167266000</v>
@@ -1649,104 +1653,108 @@
         <v>16800000</v>
       </c>
       <c r="R3" t="n">
-        <v>34544000</v>
+        <v>33333000</v>
       </c>
       <c r="S3" t="n">
-        <v>1482000</v>
+        <v>581000</v>
       </c>
       <c r="T3" t="n">
-        <v>827000</v>
-      </c>
-      <c r="U3" t="inlineStr"/>
+        <v>581000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
       <c r="V3" t="n">
-        <v>655000</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>655000</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>33062000</v>
+        <v>32752000</v>
       </c>
       <c r="Y3" t="n">
-        <v>729000</v>
+        <v>516000</v>
       </c>
       <c r="Z3" t="n">
-        <v>729000</v>
+        <v>516000</v>
       </c>
       <c r="AA3" t="n">
-        <v>20871000</v>
+        <v>22649000</v>
       </c>
       <c r="AB3" t="n">
-        <v>110000</v>
+        <v>312000</v>
       </c>
       <c r="AC3" t="n">
-        <v>20761000</v>
+        <v>22337000</v>
       </c>
       <c r="AD3" t="n">
-        <v>211474000</v>
+        <v>226557000</v>
       </c>
       <c r="AE3" t="n">
-        <v>6955000</v>
+        <v>1398000</v>
       </c>
       <c r="AF3" t="n">
-        <v>266000</v>
+        <v>98000</v>
       </c>
       <c r="AG3" t="n">
-        <v>1072000</v>
+        <v>1000000</v>
       </c>
       <c r="AH3" t="n">
-        <v>1072000</v>
+        <v>1000000</v>
       </c>
       <c r="AI3" t="n">
-        <v>5411000</v>
+        <v>300000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-3939000</v>
+        <v>-4215000</v>
       </c>
       <c r="AK3" t="n">
-        <v>9350000</v>
+        <v>4515000</v>
       </c>
       <c r="AL3" t="n">
-        <v>7052000</v>
+        <v>4207000</v>
       </c>
       <c r="AM3" t="n">
-        <v>2298000</v>
+        <v>308000</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>204519000</v>
+        <v>225159000</v>
       </c>
       <c r="AP3" t="n">
-        <v>8260000</v>
+        <v>10032000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>36822000</v>
-      </c>
-      <c r="AR3" t="inlineStr"/>
+        <v>31678000</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
       <c r="AS3" t="n">
-        <v>21937000</v>
+        <v>16241000</v>
       </c>
       <c r="AT3" t="n">
-        <v>-217000</v>
+        <v>-60000</v>
       </c>
       <c r="AU3" t="n">
-        <v>22154000</v>
+        <v>16301000</v>
       </c>
       <c r="AV3" t="n">
-        <v>137239000</v>
+        <v>167208000</v>
       </c>
       <c r="AW3" t="n">
-        <v>137239000</v>
+        <v>167208000</v>
       </c>
       <c r="AX3" t="n">
-        <v>137239000</v>
+        <v>167208000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>1680000000</v>
@@ -1755,37 +1763,37 @@
         <v>1680000000</v>
       </c>
       <c r="D4" t="n">
-        <v>516000</v>
+        <v>1384000</v>
       </c>
       <c r="E4" t="n">
-        <v>193224000</v>
+        <v>176930000</v>
       </c>
       <c r="F4" t="n">
-        <v>193224000</v>
+        <v>176930000</v>
       </c>
       <c r="G4" t="n">
-        <v>192407000</v>
+        <v>171457000</v>
       </c>
       <c r="H4" t="n">
-        <v>193224000</v>
+        <v>176930000</v>
       </c>
       <c r="I4" t="n">
-        <v>516000</v>
+        <v>1384000</v>
       </c>
       <c r="J4" t="n">
-        <v>193224000</v>
+        <v>176930000</v>
       </c>
       <c r="K4" t="n">
-        <v>193224000</v>
+        <v>176930000</v>
       </c>
       <c r="L4" t="n">
-        <v>193224000</v>
+        <v>176930000</v>
       </c>
       <c r="M4" t="n">
-        <v>193224000</v>
+        <v>176930000</v>
       </c>
       <c r="N4" t="n">
-        <v>-732000</v>
+        <v>-17098000</v>
       </c>
       <c r="O4" t="n">
         <v>167266000</v>
@@ -1797,108 +1805,104 @@
         <v>16800000</v>
       </c>
       <c r="R4" t="n">
-        <v>33333000</v>
+        <v>34544000</v>
       </c>
       <c r="S4" t="n">
-        <v>581000</v>
+        <v>1482000</v>
       </c>
       <c r="T4" t="n">
-        <v>581000</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
+        <v>827000</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>655000</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>655000</v>
       </c>
       <c r="X4" t="n">
-        <v>32752000</v>
+        <v>33062000</v>
       </c>
       <c r="Y4" t="n">
-        <v>516000</v>
+        <v>729000</v>
       </c>
       <c r="Z4" t="n">
-        <v>516000</v>
+        <v>729000</v>
       </c>
       <c r="AA4" t="n">
-        <v>22649000</v>
+        <v>20871000</v>
       </c>
       <c r="AB4" t="n">
-        <v>312000</v>
+        <v>110000</v>
       </c>
       <c r="AC4" t="n">
-        <v>22337000</v>
+        <v>20761000</v>
       </c>
       <c r="AD4" t="n">
-        <v>226557000</v>
+        <v>211474000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1398000</v>
+        <v>6955000</v>
       </c>
       <c r="AF4" t="n">
-        <v>98000</v>
+        <v>266000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000000</v>
+        <v>1072000</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000000</v>
+        <v>1072000</v>
       </c>
       <c r="AI4" t="n">
-        <v>300000</v>
+        <v>5411000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-4215000</v>
+        <v>-3939000</v>
       </c>
       <c r="AK4" t="n">
-        <v>4515000</v>
+        <v>9350000</v>
       </c>
       <c r="AL4" t="n">
-        <v>4207000</v>
+        <v>7052000</v>
       </c>
       <c r="AM4" t="n">
-        <v>308000</v>
+        <v>2298000</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>225159000</v>
+        <v>204519000</v>
       </c>
       <c r="AP4" t="n">
-        <v>10032000</v>
+        <v>8260000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>31678000</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
+        <v>36822000</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>16241000</v>
+        <v>21937000</v>
       </c>
       <c r="AT4" t="n">
-        <v>-60000</v>
+        <v>-217000</v>
       </c>
       <c r="AU4" t="n">
-        <v>16301000</v>
+        <v>22154000</v>
       </c>
       <c r="AV4" t="n">
-        <v>167208000</v>
+        <v>137239000</v>
       </c>
       <c r="AW4" t="n">
-        <v>167208000</v>
+        <v>137239000</v>
       </c>
       <c r="AX4" t="n">
-        <v>167208000</v>
+        <v>137239000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>1680000000</v>
@@ -1907,37 +1911,37 @@
         <v>1680000000</v>
       </c>
       <c r="D5" t="n">
-        <v>1440000</v>
+        <v>675000</v>
       </c>
       <c r="E5" t="n">
-        <v>225688000</v>
+        <v>161471000</v>
       </c>
       <c r="F5" t="n">
-        <v>225688000</v>
+        <v>161471000</v>
       </c>
       <c r="G5" t="n">
-        <v>224149000</v>
+        <v>158767000</v>
       </c>
       <c r="H5" t="n">
-        <v>225688000</v>
+        <v>161471000</v>
       </c>
       <c r="I5" t="n">
-        <v>1440000</v>
+        <v>675000</v>
       </c>
       <c r="J5" t="n">
-        <v>225688000</v>
+        <v>161471000</v>
       </c>
       <c r="K5" t="n">
-        <v>225688000</v>
+        <v>161471000</v>
       </c>
       <c r="L5" t="n">
-        <v>225688000</v>
+        <v>161471000</v>
       </c>
       <c r="M5" t="n">
-        <v>225688000</v>
+        <v>161471000</v>
       </c>
       <c r="N5" t="n">
-        <v>31446000</v>
+        <v>-32606000</v>
       </c>
       <c r="O5" t="n">
         <v>167266000</v>
@@ -1949,101 +1953,97 @@
         <v>16800000</v>
       </c>
       <c r="R5" t="n">
-        <v>74335000</v>
+        <v>26857000</v>
       </c>
       <c r="S5" t="n">
-        <v>605000</v>
-      </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="n">
-        <v>89000</v>
-      </c>
+        <v>741000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>741000</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>516000</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>516000</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>73730000</v>
+        <v>26116000</v>
       </c>
       <c r="Y5" t="n">
-        <v>924000</v>
+        <v>675000</v>
       </c>
       <c r="Z5" t="n">
-        <v>924000</v>
+        <v>675000</v>
       </c>
       <c r="AA5" t="n">
-        <v>66561000</v>
+        <v>15510000</v>
       </c>
       <c r="AB5" t="n">
-        <v>239000</v>
+        <v>71000</v>
       </c>
       <c r="AC5" t="n">
-        <v>66322000</v>
+        <v>15439000</v>
       </c>
       <c r="AD5" t="n">
-        <v>300023000</v>
+        <v>188328000</v>
       </c>
       <c r="AE5" t="n">
-        <v>2144000</v>
+        <v>3445000</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1286000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1286000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>858000</v>
+        <v>3445000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-7408000</v>
+        <v>-6423000</v>
       </c>
       <c r="AK5" t="n">
-        <v>8266000</v>
+        <v>9868000</v>
       </c>
       <c r="AL5" t="n">
-        <v>6144000</v>
+        <v>7570000</v>
       </c>
       <c r="AM5" t="n">
-        <v>2122000</v>
+        <v>2298000</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>297879000</v>
+        <v>184883000</v>
       </c>
       <c r="AP5" t="n">
-        <v>15669000</v>
+        <v>8971000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>47988000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>35000</v>
-      </c>
+        <v>38126000</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>47915000</v>
+        <v>16173000</v>
       </c>
       <c r="AT5" t="n">
-        <v>-697000</v>
+        <v>-110000</v>
       </c>
       <c r="AU5" t="n">
-        <v>48612000</v>
+        <v>16283000</v>
       </c>
       <c r="AV5" t="n">
-        <v>186272000</v>
+        <v>121407000</v>
       </c>
       <c r="AW5" t="n">
-        <v>186272000</v>
+        <v>121407000</v>
       </c>
       <c r="AX5" t="n">
-        <v>186272000</v>
+        <v>121407000</v>
       </c>
     </row>
   </sheetData>
@@ -2194,320 +2194,320 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-18537000</v>
+        <v>31623000</v>
       </c>
       <c r="C2" t="n">
-        <v>-613000</v>
+        <v>-306000</v>
       </c>
       <c r="D2" t="n">
-        <v>121407000</v>
+        <v>186272000</v>
       </c>
       <c r="E2" t="n">
-        <v>137239000</v>
+        <v>156335000</v>
       </c>
       <c r="F2" t="n">
-        <v>-15832000</v>
+        <v>29937000</v>
       </c>
       <c r="G2" t="n">
-        <v>-709000</v>
+        <v>-2825000</v>
       </c>
       <c r="H2" t="n">
-        <v>2801000</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>833000</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-11646000</v>
+      </c>
       <c r="J2" t="n">
-        <v>2290000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1121000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1121000</v>
-      </c>
+        <v>316000</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>-610000</v>
+        <v>517000</v>
       </c>
       <c r="N2" t="n">
-        <v>3000</v>
+        <v>823000</v>
       </c>
       <c r="O2" t="n">
-        <v>-613000</v>
+        <v>-306000</v>
       </c>
       <c r="P2" t="n">
-        <v>-17924000</v>
+        <v>31929000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-58000</v>
+        <v>-18000</v>
       </c>
       <c r="R2" t="n">
-        <v>-47000</v>
+        <v>-73000</v>
       </c>
       <c r="S2" t="n">
-        <v>-2822000</v>
+        <v>49055000</v>
       </c>
       <c r="T2" t="n">
-        <v>-3192000</v>
+        <v>-1166000</v>
       </c>
       <c r="U2" t="n">
-        <v>-3661000</v>
+        <v>17366000</v>
       </c>
       <c r="V2" t="n">
-        <v>4031000</v>
+        <v>32855000</v>
       </c>
       <c r="W2" t="n">
-        <v>-2026000</v>
+        <v>-266000</v>
       </c>
       <c r="X2" t="n">
-        <v>1937000</v>
+        <v>1761000</v>
       </c>
       <c r="Y2" t="n">
-        <v>1937000</v>
+        <v>1761000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-3000</v>
+        <v>-455000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-15526000</v>
+        <v>-13617000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-31882000</v>
+        <v>-19191000</v>
       </c>
       <c r="C3" t="n">
-        <v>-4654000</v>
+        <v>-14000</v>
       </c>
       <c r="D3" t="n">
-        <v>137239000</v>
+        <v>167208000</v>
       </c>
       <c r="E3" t="n">
-        <v>167208000</v>
+        <v>186272000</v>
       </c>
       <c r="F3" t="n">
-        <v>-29969000</v>
+        <v>-19064000</v>
       </c>
       <c r="G3" t="n">
-        <v>-577000</v>
+        <v>-891000</v>
       </c>
       <c r="H3" t="n">
-        <v>-2164000</v>
+        <v>1004000</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>2490000</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
+        <v>745000</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>-4654000</v>
+        <v>259000</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>273000</v>
       </c>
       <c r="O3" t="n">
-        <v>-4654000</v>
+        <v>-14000</v>
       </c>
       <c r="P3" t="n">
-        <v>-27228000</v>
+        <v>-19177000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-387000</v>
+        <v>35000</v>
       </c>
       <c r="R3" t="n">
-        <v>-13000</v>
+        <v>-75000</v>
       </c>
       <c r="S3" t="n">
-        <v>-8425000</v>
+        <v>-5383000</v>
       </c>
       <c r="T3" t="n">
-        <v>2832000</v>
+        <v>562000</v>
       </c>
       <c r="U3" t="n">
-        <v>-2533000</v>
+        <v>-41205000</v>
       </c>
       <c r="V3" t="n">
-        <v>-8724000</v>
+        <v>35260000</v>
       </c>
       <c r="W3" t="n">
-        <v>-2231000</v>
+        <v>-122000</v>
       </c>
       <c r="X3" t="n">
-        <v>458000</v>
+        <v>523000</v>
       </c>
       <c r="Y3" t="n">
-        <v>458000</v>
+        <v>523000</v>
       </c>
       <c r="Z3" t="n">
-        <v>2000</v>
+        <v>-224000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-16349000</v>
+        <v>-32292000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-19191000</v>
+        <v>-31882000</v>
       </c>
       <c r="C4" t="n">
-        <v>-14000</v>
+        <v>-4654000</v>
       </c>
       <c r="D4" t="n">
+        <v>137239000</v>
+      </c>
+      <c r="E4" t="n">
         <v>167208000</v>
       </c>
-      <c r="E4" t="n">
-        <v>186272000</v>
-      </c>
       <c r="F4" t="n">
-        <v>-19064000</v>
+        <v>-29969000</v>
       </c>
       <c r="G4" t="n">
-        <v>-891000</v>
+        <v>-577000</v>
       </c>
       <c r="H4" t="n">
-        <v>1004000</v>
+        <v>-2164000</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>745000</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+        <v>2490000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
       <c r="M4" t="n">
-        <v>259000</v>
+        <v>-4654000</v>
       </c>
       <c r="N4" t="n">
-        <v>273000</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-14000</v>
+        <v>-4654000</v>
       </c>
       <c r="P4" t="n">
-        <v>-19177000</v>
+        <v>-27228000</v>
       </c>
       <c r="Q4" t="n">
-        <v>35000</v>
+        <v>-387000</v>
       </c>
       <c r="R4" t="n">
-        <v>-75000</v>
+        <v>-13000</v>
       </c>
       <c r="S4" t="n">
-        <v>-5383000</v>
+        <v>-8425000</v>
       </c>
       <c r="T4" t="n">
-        <v>562000</v>
+        <v>2832000</v>
       </c>
       <c r="U4" t="n">
-        <v>-41205000</v>
+        <v>-2533000</v>
       </c>
       <c r="V4" t="n">
-        <v>35260000</v>
+        <v>-8724000</v>
       </c>
       <c r="W4" t="n">
-        <v>-122000</v>
+        <v>-2231000</v>
       </c>
       <c r="X4" t="n">
-        <v>523000</v>
+        <v>458000</v>
       </c>
       <c r="Y4" t="n">
-        <v>523000</v>
+        <v>458000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-224000</v>
+        <v>2000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-32292000</v>
+        <v>-16349000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>31623000</v>
+        <v>-18537000</v>
       </c>
       <c r="C5" t="n">
-        <v>-306000</v>
+        <v>-613000</v>
       </c>
       <c r="D5" t="n">
-        <v>186272000</v>
+        <v>121407000</v>
       </c>
       <c r="E5" t="n">
-        <v>156335000</v>
+        <v>137239000</v>
       </c>
       <c r="F5" t="n">
-        <v>29937000</v>
+        <v>-15832000</v>
       </c>
       <c r="G5" t="n">
-        <v>-2825000</v>
+        <v>-709000</v>
       </c>
       <c r="H5" t="n">
-        <v>833000</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-11646000</v>
-      </c>
+        <v>2801000</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>316000</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+        <v>2290000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1121000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1121000</v>
+      </c>
       <c r="M5" t="n">
-        <v>517000</v>
+        <v>-610000</v>
       </c>
       <c r="N5" t="n">
-        <v>823000</v>
+        <v>3000</v>
       </c>
       <c r="O5" t="n">
-        <v>-306000</v>
+        <v>-613000</v>
       </c>
       <c r="P5" t="n">
-        <v>31929000</v>
+        <v>-17924000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-18000</v>
+        <v>-58000</v>
       </c>
       <c r="R5" t="n">
-        <v>-73000</v>
+        <v>-47000</v>
       </c>
       <c r="S5" t="n">
-        <v>49055000</v>
+        <v>-2822000</v>
       </c>
       <c r="T5" t="n">
-        <v>-1166000</v>
+        <v>-3192000</v>
       </c>
       <c r="U5" t="n">
-        <v>17366000</v>
+        <v>-3661000</v>
       </c>
       <c r="V5" t="n">
-        <v>32855000</v>
+        <v>4031000</v>
       </c>
       <c r="W5" t="n">
-        <v>-266000</v>
+        <v>-2026000</v>
       </c>
       <c r="X5" t="n">
-        <v>1761000</v>
+        <v>1937000</v>
       </c>
       <c r="Y5" t="n">
-        <v>1761000</v>
+        <v>1937000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-455000</v>
+        <v>-3000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-13617000</v>
+        <v>-15526000</v>
       </c>
     </row>
   </sheetData>
@@ -3017,187 +3017,187 @@
       </c>
       <c r="CU1" t="inlineStr">
         <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
         </is>
       </c>
       <c r="EF1" t="inlineStr">
@@ -3324,7 +3324,7 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.323</v>
+        <v>0.343</v>
       </c>
       <c r="AD2" t="n">
         <v>112000</v>
@@ -3333,7 +3333,7 @@
         <v>112000</v>
       </c>
       <c r="AF2" t="n">
-        <v>206400</v>
+        <v>48949</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -3375,10 +3375,10 @@
         <v>0.65032256</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.04206</v>
+        <v>0.042</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.05756</v>
+        <v>0.053915</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -3446,7 +3446,7 @@
         <v>-0.6111111</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
@@ -3553,140 +3553,140 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CU2" t="n">
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>Geotech Holdings Ltd.</t>
+        </is>
+      </c>
+      <c r="CV2" t="n">
         <v>5.000001</v>
       </c>
-      <c r="CV2" t="n">
+      <c r="CW2" t="n">
         <v>0.042</v>
       </c>
-      <c r="CW2" t="inlineStr">
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>GEOTECH HLDGS</t>
+        </is>
+      </c>
+      <c r="CZ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>1507858200000</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>0.0020000003</v>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>0.04 - 0.042</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DE2" t="n">
+        <v>1774942587</v>
+      </c>
+      <c r="DF2" t="inlineStr">
         <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="CX2" t="inlineStr">
+      <c r="DG2" t="inlineStr">
         <is>
           <t>finmb_537914706</t>
         </is>
       </c>
-      <c r="CY2" t="inlineStr">
+      <c r="DH2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="CZ2" t="inlineStr">
+      <c r="DI2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="DA2" t="n">
+      <c r="DJ2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DB2" t="inlineStr">
+      <c r="DK2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="DC2" t="b">
+      <c r="DL2" t="b">
         <v>0</v>
       </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="DE2" t="b">
+      <c r="DM2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DO2" t="b">
         <v>0</v>
       </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>GEOTECH HLDGS</t>
-        </is>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DH2" t="n">
-        <v>1774942587</v>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>Geotech Holdings Ltd.</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="DP2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DK2" t="n">
-        <v>206400</v>
-      </c>
-      <c r="DL2" t="n">
+      <c r="DQ2" t="n">
+        <v>48949</v>
+      </c>
+      <c r="DR2" t="n">
         <v>0.011</v>
       </c>
-      <c r="DM2" t="n">
+      <c r="DS2" t="n">
         <v>0.3548387</v>
       </c>
-      <c r="DN2" t="inlineStr">
+      <c r="DT2" t="inlineStr">
         <is>
           <t>0.031 - 0.155</t>
         </is>
       </c>
-      <c r="DO2" t="n">
+      <c r="DU2" t="n">
         <v>-0.113000005</v>
       </c>
-      <c r="DP2" t="n">
+      <c r="DV2" t="n">
         <v>-0.7290323</v>
       </c>
-      <c r="DQ2" t="n">
+      <c r="DW2" t="n">
         <v>-61.11111</v>
       </c>
-      <c r="DR2" t="n">
+      <c r="DX2" t="n">
         <v>1742807707</v>
       </c>
-      <c r="DS2" t="n">
+      <c r="DY2" t="n">
         <v>1742807707</v>
       </c>
-      <c r="DT2" t="b">
+      <c r="DZ2" t="b">
         <v>0</v>
       </c>
-      <c r="DU2" t="n">
+      <c r="EA2" t="n">
         <v>-0.01</v>
       </c>
-      <c r="DV2" t="n">
-        <v>-5.9999526e-05</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>-0.0014265223</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-0.015560001</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-0.27032664</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EB2" t="b">
+      <c r="EB2" t="n">
         <v>0</v>
       </c>
       <c r="EC2" t="n">
-        <v>1507858200000</v>
+        <v>0</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.0020000003</v>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>0.04 - 0.042</t>
-        </is>
+        <v>-0.011915002</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-0.22099604</v>
       </c>
       <c r="EF2" t="inlineStr"/>
     </row>
